--- a/artfynd/A 30156-2025 artfynd.xlsx
+++ b/artfynd/A 30156-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739761</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30156-2025 artfynd.xlsx
+++ b/artfynd/A 30156-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739761</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30156-2025 artfynd.xlsx
+++ b/artfynd/A 30156-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739761</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30156-2025 artfynd.xlsx
+++ b/artfynd/A 30156-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739761</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30156-2025 artfynd.xlsx
+++ b/artfynd/A 30156-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739761</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30156-2025 artfynd.xlsx
+++ b/artfynd/A 30156-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739761</v>
       </c>
       <c r="B2" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30156-2025 artfynd.xlsx
+++ b/artfynd/A 30156-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739761</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30156-2025 artfynd.xlsx
+++ b/artfynd/A 30156-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739761</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>91889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30156-2025 artfynd.xlsx
+++ b/artfynd/A 30156-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739761</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
